--- a/17 18 20/5.Power Bi/Transformation/Data.xlsx
+++ b/17 18 20/5.Power Bi/Transformation/Data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -154,13 +154,21 @@
   </si>
   <si>
     <t>nancy.lewis@email.com</t>
+  </si>
+  <si>
+    <t>INCENTIVES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <numFmts count="3">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0.0000000_ ;_ * \-#,##0.0000000_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="170" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +197,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -207,11 +229,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -222,14 +245,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Comma" xfId="2" builtinId="3"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -509,18 +540,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.21875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -534,13 +566,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="2">
         <v>101</v>
       </c>
@@ -553,14 +588,17 @@
       <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="5">
+        <v>1.6500165001650016</v>
+      </c>
+      <c r="F2" s="2">
         <v>55000</v>
       </c>
-      <c r="F2" s="4">
+      <c r="G2" s="7">
         <v>44211</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="2">
         <v>102</v>
       </c>
@@ -573,14 +611,17 @@
       <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="5">
+        <v>1.8000180001800019</v>
+      </c>
+      <c r="F3" s="2">
         <v>60000</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G3" s="7">
         <v>43912</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" s="2">
         <v>103</v>
       </c>
@@ -593,14 +634,17 @@
       <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="5">
+        <v>2.1000210002100022</v>
+      </c>
+      <c r="F4" s="2">
         <v>70000</v>
       </c>
-      <c r="F4" s="4">
+      <c r="G4" s="7">
         <v>43656</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" s="2">
         <v>104</v>
       </c>
@@ -611,14 +655,17 @@
         <v>16</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="2">
+      <c r="E5" s="5">
+        <v>1.950019500195002</v>
+      </c>
+      <c r="F5" s="2">
         <v>65000</v>
       </c>
-      <c r="F5" s="4">
+      <c r="G5" s="7">
         <v>44597</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="2">
         <v>105</v>
       </c>
@@ -631,12 +678,15 @@
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="4">
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="7">
         <v>44426</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7" s="2">
         <v>106</v>
       </c>
@@ -649,14 +699,17 @@
       <c r="D7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="5">
+        <v>1.7400174001740016</v>
+      </c>
+      <c r="F7" s="2">
         <v>58000</v>
       </c>
-      <c r="F7" s="4">
+      <c r="G7" s="7">
         <v>44177</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="2">
         <v>107</v>
       </c>
@@ -669,14 +722,17 @@
       <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="5">
+        <v>1.6500165001650016</v>
+      </c>
+      <c r="F8" s="2">
         <v>55000</v>
       </c>
-      <c r="F8" s="4">
+      <c r="G8" s="7">
         <v>44211</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9" s="2">
         <v>108</v>
       </c>
@@ -689,14 +745,17 @@
       <c r="D9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="5">
+        <v>2.1600216002160022</v>
+      </c>
+      <c r="F9" s="2">
         <v>72000</v>
       </c>
-      <c r="F9" s="4">
+      <c r="G9" s="7">
         <v>45086</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10" s="2">
         <v>109</v>
       </c>
@@ -709,14 +768,17 @@
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="5">
+        <v>1.8300183001830019</v>
+      </c>
+      <c r="F10" s="2">
         <v>61000</v>
       </c>
-      <c r="F10" s="4">
+      <c r="G10" s="7">
         <v>44665</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" s="2">
         <v>110</v>
       </c>
@@ -729,14 +791,17 @@
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="5">
+        <v>2.0400204002040021</v>
+      </c>
+      <c r="F11" s="2">
         <v>68000</v>
       </c>
-      <c r="F11" s="4">
+      <c r="G11" s="7">
         <v>43432</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" s="2">
         <v>111</v>
       </c>
@@ -747,14 +812,17 @@
         <v>13</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2">
+      <c r="E12" s="5">
+        <v>2.1900219002190022</v>
+      </c>
+      <c r="F12" s="2">
         <v>73000</v>
       </c>
-      <c r="F12" s="4">
+      <c r="G12" s="7">
         <v>44456</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" s="2">
         <v>112</v>
       </c>
@@ -767,14 +835,17 @@
       <c r="D13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="5">
+        <v>1.6800168001680016</v>
+      </c>
+      <c r="F13" s="2">
         <v>56000</v>
       </c>
-      <c r="F13" s="4">
+      <c r="G13" s="7">
         <v>44456</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" s="2">
         <v>113</v>
       </c>
@@ -787,14 +858,17 @@
       <c r="D14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="5">
+        <v>1.7700177001770017</v>
+      </c>
+      <c r="F14" s="2">
         <v>59000</v>
       </c>
-      <c r="F14" s="4">
+      <c r="G14" s="7">
         <v>43833</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" s="2">
         <v>114</v>
       </c>
@@ -807,12 +881,15 @@
       <c r="D15" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="4">
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="7">
         <v>44706</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="2">
         <v>115</v>
       </c>
@@ -825,18 +902,21 @@
       <c r="D16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="5">
+        <v>2.0100201002010021</v>
+      </c>
+      <c r="F16" s="2">
         <v>67000</v>
       </c>
-      <c r="F16" s="4">
+      <c r="G16" s="7">
         <v>43768</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:7">
       <c r="A17" s="2">
         <v>116</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -845,18 +925,21 @@
       <c r="D17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="5">
+        <v>2.1300213002130022</v>
+      </c>
+      <c r="F17" s="2">
         <v>71000</v>
       </c>
-      <c r="F17" s="4">
+      <c r="G17" s="7">
         <v>44968</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:7">
       <c r="A18" s="2">
         <v>117</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
@@ -865,18 +948,21 @@
       <c r="D18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="5">
+        <v>1.860018600186002</v>
+      </c>
+      <c r="F18" s="2">
         <v>62000</v>
       </c>
-      <c r="F18" s="4">
+      <c r="G18" s="7">
         <v>44378</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:7">
       <c r="A19" s="2">
         <v>118</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -885,14 +971,17 @@
       <c r="D19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="5">
+        <v>1.6200162001620015</v>
+      </c>
+      <c r="F19" s="2">
         <v>54000</v>
       </c>
-      <c r="F19" s="4">
+      <c r="G19" s="7">
         <v>44968</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:7">
       <c r="A20" s="2">
         <v>119</v>
       </c>
@@ -905,14 +994,17 @@
       <c r="D20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="5">
+        <v>1.890018900189002</v>
+      </c>
+      <c r="F20" s="2">
         <v>63000</v>
       </c>
-      <c r="F20" s="4">
+      <c r="G20" s="7">
         <v>43909</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:7">
       <c r="A21" s="2">
         <v>120</v>
       </c>
@@ -925,10 +1017,13 @@
       <c r="D21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="5">
+        <v>2.1300213002130022</v>
+      </c>
+      <c r="F21" s="2">
         <v>71000</v>
       </c>
-      <c r="F21" s="4">
+      <c r="G21" s="7">
         <v>44968</v>
       </c>
     </row>
